--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260922.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.64%</t>
+          <t>26.75%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.92%</t>
+          <t>7.93%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.89%</t>
+          <t>7.91%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.97%</t>
+          <t>7.09%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.11%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.36%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>20,345</t>
+          <t>31,430</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>31,430</t>
+          <t>20,345</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -924,29 +924,29 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>19,490</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -968,24 +968,24 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>7,990</t>
+          <t>19,490</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1144,46 +1144,46 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>126,205</t>
+          <t>15,871</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,871</t>
+          <t>126,205</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>48,462,970</t>
+          <t>48,407,970</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>610,404</t>
+          <t>634,161</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
